--- a/tools/excel/ccb/mapping-ccb-cff-2023-03-01-and-ccb-cyfun2025.xlsx
+++ b/tools/excel/ccb/mapping-ccb-cff-2023-03-01-and-ccb-cyfun2025.xlsx
@@ -453,10 +453,8 @@
           <t>version</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -503,7 +501,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mapping between CCB CyberFundamentals Framework - 2023-03-01 and CyberFundamentals 2025</t>
+          <t>Mapping between CCB CyberFundamentals Framework - 2023-03-01 and CyberFundamentals 2025
+Aligned on the CCB transposition table v2026-02-25: https://cyfun.eu/sites/default/files/2026-03/Mapping_CyFun2023-CyFun2025_v2026-02-25.xlsx</t>
         </is>
       </c>
     </row>
@@ -688,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E355"/>
+  <dimension ref="A1:E196"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="17.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -725,6023 +724,3479 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASIC_DE.AE-3.1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DE.AE-03.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BASIC_DE.CM-1.1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DE.CM-01.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BASIC_DE.CM-3.1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DE.CM-03-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BASIC_DE.CM-4.1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DE.CM-01.2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>BASIC_ID.AM-1.1</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ID.AM-01.1</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.AM-1.1</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BASIC_ID.AM-2.1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ID.AM-02.1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BASIC_ID.AM-3.1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ID.AM-07.1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BASIC_ID.AM-5.1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ID.AM-05.1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BASIC_ID.GV-1.1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GV.PO-01.1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BASIC_ID.GV-3.1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GV.OC-03.1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BASIC_ID.GV-4.1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GV.RM-03.1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BASIC_ID.RA-1.1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ID.RA-01.1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BASIC_ID.RA-5.1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ID.RA-05.1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-1.1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PR.AA-01.1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-2.1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PR.AA-06.1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-3.1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PR.AA-03.1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-3.2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PR.AA-03.2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-4.1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PR.AA-05.1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-4.2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PR.AA-05.2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-4.3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PR.AA-05.3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-4.4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PR.AA-05.4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-5.1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PR.IR-01.1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AC-5.2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PR.IR-01.2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BASIC_PR.AT-1.1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PR.AT-01.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BASIC_PR.DS-3.1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PR.DS-01.9</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BASIC_PR.IP-11.1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GV.RR-04.1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BASIC_PR.IP-4.1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PR.DS-11.1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BASIC_PR.MA-1.1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ID.AM-08.2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASIC_PR.PT-1.1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PR.PS-04.1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASIC_PR.PT-4.1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PR.PS-05.1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASIC_RC.RP-1.1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RC.RP-01.1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BASIC_RS.CO-3.1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RS.CO-02.1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BASIC_RS.IM-1.1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ID.IM-03.1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BASIC_RS.RP-1.1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RS.MA-01.1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DE.AE-2.2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DE.AE-02.2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DE.AE-3.3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DE.AE-03.3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DE.AE-4.1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DE.AE-04.1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DE.CM-1.3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DE.CM-01.4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DE.CM-2.2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DE.CM-02.2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DE.CM-4.2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DE.CM-09.4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DE.CM-7.2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PR.PS-01.5</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DE.DP-5.2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ID.IM-03.9</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ID.AM-1.4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ID.AM-01.4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ID.AM-2.5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ID.AM-02.5</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ID.AM-3.3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ID.AM-03-3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ID.AM-4.2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ID.AM-04.2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ID.AM-6.2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GV.RR-02.2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ID.BE-1.2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GV.SC-01.1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ID.BE-5.2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GV.OC-04.3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ID.BE-5.3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>GV.OC-04.4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ID.RA-1.3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ID.RA-01.4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ID.RA-2.2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ID.RA-02.2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ID.RA-5.3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ID.RA-05.3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ID.SC-2.2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GV.SC-07.2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ID.SC-3.2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GV.SC-05.2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ID.SC-3.3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GV.SC-05.3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ID.SC-4.2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GV.SC-07.4</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.AE-2.1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DE.AE-02.1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.AE-3.2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DE.AE-03.2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.AE-5.1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>DE.AE-08.1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.CM-1.2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DE.CM-01.3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.CM-2.1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DE.CM-02.1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.CM-3.2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>DE.CM-03-2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.CM-3.3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PR.PS-02.1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.CM-5.1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DE.CM-09.1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.CM-6.1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DE.CM-06.1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.CM-6.2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>DE.CM-06.2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.CM-8.1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ID.RA-01.5</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>IMPORTANT_DE.DP-4.1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DE.AE-06.1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.AM-1.2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>ID.AM-01.2</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.AM-1.3</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ID.AM-01.3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.AM-2.2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ID.AM-02.2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-1.2</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-01.2</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.AM-2.3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ID.AM-02.3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-1.3</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-01.3</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.AM-2.4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ID.AM-02.4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-1.4</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-01.4</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.AM-3.2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ID.AM-03-2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.AM-2.1</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.1</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.AM-4.1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ID.AM-04.1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.AM-6.1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GV.RR-02.1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.AM-2.1</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.2</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.BE-1.1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GV.OC-05.1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-2.2</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.2</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.BE-2.1</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GV.OC-01.1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-2.2</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.1</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.BE-4.1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GV.OC-04.1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-2.3</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.3</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.BE-5.1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GV.OC-04.2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.GV-1.2</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GV.PO-01.2</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.GV-3.2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GV.OC-03.2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.GV-4.2</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GV.RM-03.2</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.RA-1.2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ID.RA-01.2</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-2.4</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.4</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.RA-2.1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ID.RA-02.1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-2.5</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.5</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.RA-5.2</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ID.RA-05.2</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.AM-3.1</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-03-3</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.RA-6.1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ID.RA-06.1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.AM-3.1</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-03-2</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.RM-1.1</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GV.RM-01.1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-3.2</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-03-3</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.RM-2.1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>GV.RM-02.1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-3.2</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-03-2</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.SC-2.1</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>GV.SC-07.1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-3.3</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-03-3</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.SC-3.1</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>GV.SC-05.1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-3.3</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-03-2</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>IMPORTANT_ID.SC-5.1</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GV.SC-08.1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-4.1</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.1</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AC-1.2</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PR.AA-01.2</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-4.1</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-04.2</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AC-2.2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PR.AA-06.2</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-4.2</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-03-3</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AC-3.3</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PR.AA-03.3</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-4.2</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-03-2</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AC-4.5</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PR.AA-05.5</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.AM-5.1</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-05.1</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AC-4.6</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PR.AA-05.6</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.AM-6.1</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-02.1</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AC-4.7</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PR.AA-05.7</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-6.2</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-02.2</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AC-5.3</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PR.IR-01.3</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AC-5.4</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PR.IR-01.4</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.BE-1.1</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-04.2</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AC-6.1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PR.AA-02.1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AT-1.2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PR.AT-01.2</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AT-2.1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PR.AT-02.3</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AT-3.2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>GV.SC-02.1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AT-4.1</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PR.AT-02.1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.BE-1.1</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-05.1</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.AT-5.1</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PR.AT-02.2</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>ID.BE-1.2</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>GV.OC-05.1</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.DS-3.2</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ID.AM-08.3</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.DS-3.3</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ID.AM-08.4</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.DS-4.1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PR.IR-04.1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.DS-4.2</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PR.PS-04.3</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.DS-5.1</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RS.MI-01.2</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>ID.BE-1.2</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-01.1</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.DS-6.1</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PR.DS-01.1</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-1.1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PR.PS-01.1</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-11.2</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GV.RR-04.2</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="32" customHeight="1">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-12.1</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ID.RA-01.3</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.BE-2.1</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-08.1</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-2.1</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PR.PS-06.1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.BE-3.1</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>GV.RM-01.1</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-3.1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PR.PS-06.2</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.BE-3.1</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-05.1</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
+    <row r="120" ht="32" customHeight="1">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-4.2</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PR.DS-11.2</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-4.3</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PR.DS-11.3</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-5.1</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PR.IR-02.1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="32" customHeight="1">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-7.1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ID.IM-03.3</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.BE-4.1</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-03.1</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-8.1</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ID.IM-03.4</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="32" customHeight="1">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-8.2</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ID.IM-03.5</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-8.3</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ID.IM-03.6</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.IP-9.1</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ID.IM-04.1</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.BE-4.1</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.2</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
+    <row r="128" ht="32" customHeight="1">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.MA-1.2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ID.AM-08.6</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.MA-1.3</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ID.AM-08.8</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.MA-1.4</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PR.PS-03.1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.BE-5.1</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>GV.OC-04.3</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.MA-2.1</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ID.AM-08.11</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.BE-5.1</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>GV.OC-04.4</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
+    <row r="132" ht="32" customHeight="1">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.MA-2.2</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ID.AM-08.12</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>ID.BE-5.2</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>GV.OC-04.3</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
+    <row r="133" ht="32" customHeight="1">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.PT-1.2</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PR.PS-04.2</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="32" customHeight="1">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.PT-2.1</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PR.DS-01.4</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="32" customHeight="1">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>IMPORTANT_PR.PT-2.2</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PR.DS-01.5</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>ID.BE-5.2</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-03.1</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
+    <row r="136" ht="32" customHeight="1">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RC.CO-1.1</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RC.CO-04.1</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>ID.BE-5.3</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>GV.OC-04.4</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RC.CO-3.1</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RC.CO-03.1</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="32" customHeight="1">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RC.IM-1.1</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ID.IM-03.2</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="32" customHeight="1">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RS.AN-1.1</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RS.MA-02.1</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RS.AN-2.1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RS.MA-03.1</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RS.AN-5.1</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ID.RA-08.1</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="32" customHeight="1">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RS.CO-1.1</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PR.AT-01.3</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="32" customHeight="1">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RS.CO-3.2</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>RS.CO-02.2</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="32" customHeight="1">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RS.CO-4.1</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RS.MA-01.2</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.GV-1.1</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>GV.PO-01.1</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
+    <row r="145" ht="32" customHeight="1">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RS.IM-2.1</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>GV.RR-03-2</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>IMPORTANT_RS.MI-1.1</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>RS.MI-01.1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PR.AC-1.3</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PR.AA-01.3</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.GV-1.2</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>GV.PO-01.1</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>PR.AC-1.4</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PR.AA-01.4</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.GV-1.2</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>GV.PO-01.2</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>PR.AC-1.5</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PR.AA-01.5</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="32" customHeight="1">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PR.AC-2.3</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PR.AA-06.3</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="32" customHeight="1">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PR.AC-2.4</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PR.AA-06.4</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="32" customHeight="1">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PR.AC-4.8</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PR.AA-05.8</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="32" customHeight="1">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PR.AC-4.9</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PR.AA-05.9</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PR.AC-5.5</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PR.IR-01.5</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.GV-3.1</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>GV.OC-03.1</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PR.AC-5.6</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PR.IR-01.6</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.GV-3.1</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>GV.OC-03.2</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
+    <row r="156" ht="32" customHeight="1">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PR.AC-6.2</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PR.AA-02.2</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.GV-3.2</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>GV.OC-03.2</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
+    <row r="157" ht="32" customHeight="1">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>PR.AT-1.3</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PR.AT-01.4</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.GV-4.1</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>GV.RM-03.1</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
+    <row r="158" ht="32" customHeight="1">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>PR.AT-3.4</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>GV.SC-07.3</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.GV-4.1</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>GV.PO-01.1</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
+    <row r="159" ht="16" customHeight="1">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PR.DS-1.1</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PR.DS-01.6</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.GV-4.2</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>GV.PO-01.1</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
+    <row r="160" ht="16" customHeight="1">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PR.DS-2.1</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PR.DS-02.2</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.GV-4.2</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>GV.RM-03.2</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
+    <row r="161" ht="32" customHeight="1">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PR.DS-3.4</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ID.AM-08.5</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="32" customHeight="1">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>PR.DS-4.3</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PR.DS-10.1</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>PR.DS-6.2</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PR.DS-01.2</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="32" customHeight="1">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PR.DS-6.3</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PR.DS-01.3</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PR.DS-7.1</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PR.IR-01.7</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>PR.DS-8.1</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>DE.CM-09.2</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>PR.DS-8.2</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>DE.CM-09.3</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>PR.IP-1.2</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PR.PS-01.2</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PR.IP-2.2</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PR.PS-06.3</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.RA-1.1</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-01.1</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
+    <row r="170" ht="16" customHeight="1">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PR.IP-3.2</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PR.PS-06.4</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RA-1.2</t>
-        </is>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-01.2</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
+    <row r="171" ht="16" customHeight="1">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>PR.IP-4.4</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PR.DS-11.4</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="16" customHeight="1">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PR.IP-4.5</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PR.DS-11.5</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RA-1.2</t>
-        </is>
-      </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-01.3</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
+    <row r="173" ht="16" customHeight="1">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PR.IP-5.2</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PR.IR-02.2</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-1.3</t>
-        </is>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-01.4</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
+    <row r="174" ht="32" customHeight="1">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PR.IP-7.2</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ID.IM-03.7</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="32" customHeight="1">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PR.IP-7.3</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ID.IM-03.8</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RA-2.1</t>
-        </is>
-      </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-02.1</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
+    <row r="176" ht="16" customHeight="1">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>PR.IP-9.2</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ID.IM-04.2</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PR.MA-1.5</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ID.AM-08.7</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-2.2</t>
-        </is>
-      </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-02.2</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
+    <row r="178" ht="32" customHeight="1">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PR.MA-1.6</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ID.AM-08.9</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_ID.RA-5.1</t>
-        </is>
-      </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-05.1</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
+    <row r="179" ht="32" customHeight="1">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PR.MA-1.7</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D.AM-08.10</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RA-5.2</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-05.2</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PR.MA-2.3</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ID.AM-08.13</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-5.3</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-05.3</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
+    <row r="181" ht="16" customHeight="1">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>PR.PT-1.3</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PR.PS-04.4</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RA-6.1</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-05.3</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
+    <row r="182" ht="32" customHeight="1">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PR.PT-1.4</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PR.PS-04.5</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="32" customHeight="1">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>PR.PT-2.3</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PR.DS-02.1</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="16" customHeight="1">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>PR.PT-3.2</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PR.PS-01.3</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="16" customHeight="1">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PR.PT-3.3</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PR.PS-01.4</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="16" customHeight="1">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>PR.PT-4.2</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PR.IR-01.8</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RA-6.1</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-06.1</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
+    <row r="187" ht="32" customHeight="1">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>PR.PT-4.3</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PR.IR-01.9</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="32" customHeight="1">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>R.AC-3.4</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PR.AA-03.4</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="16" customHeight="1">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>R.AC-3.5</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>PR.AA-03.5</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="16" customHeight="1">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>RC.CO-1.2</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>RC.CO-04.2</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RM-1.1</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>GV.RM-03.2</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
+    <row r="191" ht="16" customHeight="1">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>RC.CO-2.1</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>RC.CO-04.3</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RM-1.1</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>GV.RM-03.1</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>RC.RP-1.2</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>RC.RP-02.1</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="32" customHeight="1">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>RS.AN-1.2</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>RS.MA-02.2</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RM-2.1</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>GV.RM-02.1</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.RM-3.1</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-05.1</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
+    <row r="194" ht="32" customHeight="1">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>RS.AN-3.1</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>RS.AN-06.1</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-1.1</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-01.1</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
+    <row r="195" ht="16" customHeight="1">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>RS.AN-3.2</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>RS.AN-03.1</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-1.1</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-10.1</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
+    <row r="196" ht="32" customHeight="1">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>RS.AN-5.2</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ID.RA-08.2</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
         <is>
           <t>intersect</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.SC-2.1</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-01.1</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.SC-2.1</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.4</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-2.2</t>
-        </is>
-      </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.2</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-2.2</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.4</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.SC-3.1</t>
-        </is>
-      </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-05.3</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.SC-3.1</t>
-        </is>
-      </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-05.2</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-3.2</t>
-        </is>
-      </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-05.2</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-3.3</t>
-        </is>
-      </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-05.3</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.SC-4.1</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.4</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.SC-4.1</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.3</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-4.2</t>
-        </is>
-      </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.4</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-4.2</t>
-        </is>
-      </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.3</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.SC-5.1</t>
-        </is>
-      </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-08.1</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_ID.SC-5.1</t>
-        </is>
-      </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-04.2</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-5.2</t>
-        </is>
-      </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-08.1</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="1" t="inlineStr">
-        <is>
-          <t>ID.SC-5.2</t>
-        </is>
-      </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-04.2</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-1.1</t>
-        </is>
-      </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-01.2</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-1.1</t>
-        </is>
-      </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-01.1</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-1.2</t>
-        </is>
-      </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-01.2</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="1" t="inlineStr">
-        <is>
-          <t>PR.AC-1.3</t>
-        </is>
-      </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-01.3</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="1" t="inlineStr">
-        <is>
-          <t>PR.AC-1.4</t>
-        </is>
-      </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-01.4</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="1" t="inlineStr">
-        <is>
-          <t>PR.AC-1.5</t>
-        </is>
-      </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-01.5</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-2.1</t>
-        </is>
-      </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-06.2</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-2.1</t>
-        </is>
-      </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-06.4</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="32" customHeight="1">
-      <c r="A92" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-2.2</t>
-        </is>
-      </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-06.2</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="1" t="inlineStr">
-        <is>
-          <t>PR.AC-2.3</t>
-        </is>
-      </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-06.3</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>PR.AC-2.4</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-06.4</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-3.1</t>
-        </is>
-      </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.1</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-3.1</t>
-        </is>
-      </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.3</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-3.2</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.2</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="32" customHeight="1">
-      <c r="A98" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-3.3</t>
-        </is>
-      </c>
-      <c r="B98" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.3</t>
-        </is>
-      </c>
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="32" customHeight="1">
-      <c r="A99" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-3.3</t>
-        </is>
-      </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.4</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="1" t="inlineStr">
-        <is>
-          <t>R.AC-3.4</t>
-        </is>
-      </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.4</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>R.AC-3.5</t>
-        </is>
-      </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.5</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>R.AC-3.5</t>
-        </is>
-      </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.3</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-4.1</t>
-        </is>
-      </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.7</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-4.1</t>
-        </is>
-      </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.9</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-4.2</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.2</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-4.3</t>
-        </is>
-      </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.4</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-4.3</t>
-        </is>
-      </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.3</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-4.4</t>
-        </is>
-      </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.4</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-4.5</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.5</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-4.6</t>
-        </is>
-      </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.6</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-4.7</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.7</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>PR.AC-4.8</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.8</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t>PR.AC-4.9</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.9</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-5.1</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.1</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-5.2</t>
-        </is>
-      </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.2</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AC-5.2</t>
-        </is>
-      </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.3</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="32" customHeight="1">
-      <c r="A117" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-5.3</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.2</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-5.3</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.3</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="32" customHeight="1">
-      <c r="A119" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-5.4</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.4</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="32" customHeight="1">
-      <c r="A120" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-5.4</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.2</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="1" t="inlineStr">
-        <is>
-          <t>PR.AC-5.5</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.5</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="1" t="inlineStr">
-        <is>
-          <t>PR.AC-5.6</t>
-        </is>
-      </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.6</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="32" customHeight="1">
-      <c r="A123" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-6.1</t>
-        </is>
-      </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-02.1</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-7.1</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-01.4</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="32" customHeight="1">
-      <c r="A125" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AC-7.1</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-02.2</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AT-1.1</t>
-        </is>
-      </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-01.1</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.AT-1.1</t>
-        </is>
-      </c>
-      <c r="B127" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-01.4</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="32" customHeight="1">
-      <c r="A128" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-1.2</t>
-        </is>
-      </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-01.2</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="32" customHeight="1">
-      <c r="A129" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-1.2</t>
-        </is>
-      </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-01.4</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-1.3</t>
-        </is>
-      </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-01.4</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-1.3</t>
-        </is>
-      </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.5</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="32" customHeight="1">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-2.1</t>
-        </is>
-      </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-02.3</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="32" customHeight="1">
-      <c r="A133" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-2.1</t>
-        </is>
-      </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-05.9</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="32" customHeight="1">
-      <c r="A134" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-3.1</t>
-        </is>
-      </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.3</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="32" customHeight="1">
-      <c r="A135" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-3.1</t>
-        </is>
-      </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.4</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="32" customHeight="1">
-      <c r="A136" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-3.2</t>
-        </is>
-      </c>
-      <c r="B136" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-02.1</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="32" customHeight="1">
-      <c r="A137" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-3.2</t>
-        </is>
-      </c>
-      <c r="B137" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.3</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="32" customHeight="1">
-      <c r="A138" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-3.3</t>
-        </is>
-      </c>
-      <c r="B138" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.3</t>
-        </is>
-      </c>
-      <c r="C138" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="32" customHeight="1">
-      <c r="A139" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-3.3</t>
-        </is>
-      </c>
-      <c r="B139" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.4</t>
-        </is>
-      </c>
-      <c r="C139" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-3.4</t>
-        </is>
-      </c>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.3</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-3.4</t>
-        </is>
-      </c>
-      <c r="B141" s="1" t="inlineStr">
-        <is>
-          <t>GV.SC-07.4</t>
-        </is>
-      </c>
-      <c r="C141" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="32" customHeight="1">
-      <c r="A142" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-4.1</t>
-        </is>
-      </c>
-      <c r="B142" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-02.2</t>
-        </is>
-      </c>
-      <c r="C142" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="32" customHeight="1">
-      <c r="A143" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-4.1</t>
-        </is>
-      </c>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-02.1</t>
-        </is>
-      </c>
-      <c r="C143" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="32" customHeight="1">
-      <c r="A144" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-5.1</t>
-        </is>
-      </c>
-      <c r="B144" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-01.3</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="32" customHeight="1">
-      <c r="A145" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.AT-5.1</t>
-        </is>
-      </c>
-      <c r="B145" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-02.1</t>
-        </is>
-      </c>
-      <c r="C145" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-1.1</t>
-        </is>
-      </c>
-      <c r="B146" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-01.6</t>
-        </is>
-      </c>
-      <c r="C146" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-2.1</t>
-        </is>
-      </c>
-      <c r="B147" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-02.2</t>
-        </is>
-      </c>
-      <c r="C147" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="16" customHeight="1">
-      <c r="A148" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.DS-3.1</t>
-        </is>
-      </c>
-      <c r="B148" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-01.9</t>
-        </is>
-      </c>
-      <c r="C148" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.DS-3.1</t>
-        </is>
-      </c>
-      <c r="B149" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.4</t>
-        </is>
-      </c>
-      <c r="C149" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="32" customHeight="1">
-      <c r="A150" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-3.2</t>
-        </is>
-      </c>
-      <c r="B150" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.3</t>
-        </is>
-      </c>
-      <c r="C150" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="32" customHeight="1">
-      <c r="A151" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-3.2</t>
-        </is>
-      </c>
-      <c r="B151" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.4</t>
-        </is>
-      </c>
-      <c r="C151" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="32" customHeight="1">
-      <c r="A152" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-3.3</t>
-        </is>
-      </c>
-      <c r="B152" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.4</t>
-        </is>
-      </c>
-      <c r="C152" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="32" customHeight="1">
-      <c r="A153" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-3.3</t>
-        </is>
-      </c>
-      <c r="B153" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.3</t>
-        </is>
-      </c>
-      <c r="C153" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-3.4</t>
-        </is>
-      </c>
-      <c r="B154" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.5</t>
-        </is>
-      </c>
-      <c r="C154" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-3.4</t>
-        </is>
-      </c>
-      <c r="B155" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.3</t>
-        </is>
-      </c>
-      <c r="C155" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="32" customHeight="1">
-      <c r="A156" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-4.1</t>
-        </is>
-      </c>
-      <c r="B156" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-04.1</t>
-        </is>
-      </c>
-      <c r="C156" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="32" customHeight="1">
-      <c r="A157" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-4.2</t>
-        </is>
-      </c>
-      <c r="B157" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-04.1</t>
-        </is>
-      </c>
-      <c r="C157" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="32" customHeight="1">
-      <c r="A158" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-4.2</t>
-        </is>
-      </c>
-      <c r="B158" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-04.3</t>
-        </is>
-      </c>
-      <c r="C158" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="16" customHeight="1">
-      <c r="A159" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-4.3</t>
-        </is>
-      </c>
-      <c r="B159" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-04.1</t>
-        </is>
-      </c>
-      <c r="C159" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="16" customHeight="1">
-      <c r="A160" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-4.3</t>
-        </is>
-      </c>
-      <c r="B160" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-10.1</t>
-        </is>
-      </c>
-      <c r="C160" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="32" customHeight="1">
-      <c r="A161" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-5.1</t>
-        </is>
-      </c>
-      <c r="B161" s="1" t="inlineStr">
-        <is>
-          <t>RS.MI-01.2</t>
-        </is>
-      </c>
-      <c r="C161" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="32" customHeight="1">
-      <c r="A162" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-5.1</t>
-        </is>
-      </c>
-      <c r="B162" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-10.1</t>
-        </is>
-      </c>
-      <c r="C162" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="32" customHeight="1">
-      <c r="A163" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-6.1</t>
-        </is>
-      </c>
-      <c r="B163" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.2</t>
-        </is>
-      </c>
-      <c r="C163" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="32" customHeight="1">
-      <c r="A164" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.DS-6.1</t>
-        </is>
-      </c>
-      <c r="B164" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-01.1</t>
-        </is>
-      </c>
-      <c r="C164" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="16" customHeight="1">
-      <c r="A165" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-6.2</t>
-        </is>
-      </c>
-      <c r="B165" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.2</t>
-        </is>
-      </c>
-      <c r="C165" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="16" customHeight="1">
-      <c r="A166" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-6.2</t>
-        </is>
-      </c>
-      <c r="B166" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-01.4</t>
-        </is>
-      </c>
-      <c r="C166" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-6.3</t>
-        </is>
-      </c>
-      <c r="B167" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.2</t>
-        </is>
-      </c>
-      <c r="C167" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="16" customHeight="1">
-      <c r="A168" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-6.3</t>
-        </is>
-      </c>
-      <c r="B168" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.4</t>
-        </is>
-      </c>
-      <c r="C168" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-7.1</t>
-        </is>
-      </c>
-      <c r="B169" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.7</t>
-        </is>
-      </c>
-      <c r="C169" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="16" customHeight="1">
-      <c r="A170" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-8.1</t>
-        </is>
-      </c>
-      <c r="B170" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.2</t>
-        </is>
-      </c>
-      <c r="C170" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="16" customHeight="1">
-      <c r="A171" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-8.1</t>
-        </is>
-      </c>
-      <c r="B171" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.3</t>
-        </is>
-      </c>
-      <c r="C171" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="16" customHeight="1">
-      <c r="A172" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-8.2</t>
-        </is>
-      </c>
-      <c r="B172" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.2</t>
-        </is>
-      </c>
-      <c r="C172" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="16" customHeight="1">
-      <c r="A173" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-8.2</t>
-        </is>
-      </c>
-      <c r="B173" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.3</t>
-        </is>
-      </c>
-      <c r="C173" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="32" customHeight="1">
-      <c r="A174" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-1.1</t>
-        </is>
-      </c>
-      <c r="B174" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.1</t>
-        </is>
-      </c>
-      <c r="C174" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="32" customHeight="1">
-      <c r="A175" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-1.1</t>
-        </is>
-      </c>
-      <c r="B175" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.2</t>
-        </is>
-      </c>
-      <c r="C175" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-1.2</t>
-        </is>
-      </c>
-      <c r="B176" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.2</t>
-        </is>
-      </c>
-      <c r="C176" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="16" customHeight="1">
-      <c r="A177" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-1.2</t>
-        </is>
-      </c>
-      <c r="B177" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.1</t>
-        </is>
-      </c>
-      <c r="C177" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="32" customHeight="1">
-      <c r="A178" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-2.1</t>
-        </is>
-      </c>
-      <c r="B178" s="1" t="inlineStr">
-        <is>
-          <t>D.AM-08.10</t>
-        </is>
-      </c>
-      <c r="C178" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="32" customHeight="1">
-      <c r="A179" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-2.1</t>
-        </is>
-      </c>
-      <c r="B179" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.6</t>
-        </is>
-      </c>
-      <c r="C179" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-2.2</t>
-        </is>
-      </c>
-      <c r="B180" s="1" t="inlineStr">
-        <is>
-          <t>D.AM-08.10</t>
-        </is>
-      </c>
-      <c r="C180" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="16" customHeight="1">
-      <c r="A181" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-2.2</t>
-        </is>
-      </c>
-      <c r="B181" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.6</t>
-        </is>
-      </c>
-      <c r="C181" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="32" customHeight="1">
-      <c r="A182" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-3.1</t>
-        </is>
-      </c>
-      <c r="B182" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.5</t>
-        </is>
-      </c>
-      <c r="C182" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="32" customHeight="1">
-      <c r="A183" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-3.1</t>
-        </is>
-      </c>
-      <c r="B183" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.2</t>
-        </is>
-      </c>
-      <c r="C183" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-3.2</t>
-        </is>
-      </c>
-      <c r="B184" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.5</t>
-        </is>
-      </c>
-      <c r="C184" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="16" customHeight="1">
-      <c r="A185" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-3.2</t>
-        </is>
-      </c>
-      <c r="B185" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.8</t>
-        </is>
-      </c>
-      <c r="C185" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="16" customHeight="1">
-      <c r="A186" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.IP-4.1</t>
-        </is>
-      </c>
-      <c r="B186" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-11.1</t>
-        </is>
-      </c>
-      <c r="C186" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="32" customHeight="1">
-      <c r="A187" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-4.2</t>
-        </is>
-      </c>
-      <c r="B187" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-11.2</t>
-        </is>
-      </c>
-      <c r="C187" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="32" customHeight="1">
-      <c r="A188" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-4.3</t>
-        </is>
-      </c>
-      <c r="B188" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-11.3</t>
-        </is>
-      </c>
-      <c r="C188" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="16" customHeight="1">
-      <c r="A189" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-4.4</t>
-        </is>
-      </c>
-      <c r="B189" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-11.4</t>
-        </is>
-      </c>
-      <c r="C189" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="16" customHeight="1">
-      <c r="A190" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-4.4</t>
-        </is>
-      </c>
-      <c r="B190" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-11.1</t>
-        </is>
-      </c>
-      <c r="C190" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="16" customHeight="1">
-      <c r="A191" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-4.5</t>
-        </is>
-      </c>
-      <c r="B191" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-11.5</t>
-        </is>
-      </c>
-      <c r="C191" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-4.5</t>
-        </is>
-      </c>
-      <c r="B192" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-11.1</t>
-        </is>
-      </c>
-      <c r="C192" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="32" customHeight="1">
-      <c r="A193" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-5.1</t>
-        </is>
-      </c>
-      <c r="B193" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-02.1</t>
-        </is>
-      </c>
-      <c r="C193" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="32" customHeight="1">
-      <c r="A194" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-5.1</t>
-        </is>
-      </c>
-      <c r="B194" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-02.2</t>
-        </is>
-      </c>
-      <c r="C194" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="16" customHeight="1">
-      <c r="A195" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-5.2</t>
-        </is>
-      </c>
-      <c r="B195" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-02.2</t>
-        </is>
-      </c>
-      <c r="C195" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="32" customHeight="1">
-      <c r="A196" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-6.1</t>
-        </is>
-      </c>
-      <c r="B196" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.5</t>
-        </is>
-      </c>
-      <c r="C196" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="32" customHeight="1">
-      <c r="A197" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-6.1</t>
-        </is>
-      </c>
-      <c r="B197" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.4</t>
-        </is>
-      </c>
-      <c r="C197" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-6.2</t>
-        </is>
-      </c>
-      <c r="B198" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.5</t>
-        </is>
-      </c>
-      <c r="C198" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="16" customHeight="1">
-      <c r="A199" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-6.2</t>
-        </is>
-      </c>
-      <c r="B199" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-01.9</t>
-        </is>
-      </c>
-      <c r="C199" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="32" customHeight="1">
-      <c r="A200" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-7.1</t>
-        </is>
-      </c>
-      <c r="B200" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.5</t>
-        </is>
-      </c>
-      <c r="C200" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="32" customHeight="1">
-      <c r="A201" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-7.1</t>
-        </is>
-      </c>
-      <c r="B201" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.8</t>
-        </is>
-      </c>
-      <c r="C201" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="16" customHeight="1">
-      <c r="A202" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-7.2</t>
-        </is>
-      </c>
-      <c r="B202" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.5</t>
-        </is>
-      </c>
-      <c r="C202" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="16" customHeight="1">
-      <c r="A203" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-7.2</t>
-        </is>
-      </c>
-      <c r="B203" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.7</t>
-        </is>
-      </c>
-      <c r="C203" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="16" customHeight="1">
-      <c r="A204" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-7.3</t>
-        </is>
-      </c>
-      <c r="B204" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.8</t>
-        </is>
-      </c>
-      <c r="C204" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="32" customHeight="1">
-      <c r="A205" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-8.1</t>
-        </is>
-      </c>
-      <c r="B205" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.4</t>
-        </is>
-      </c>
-      <c r="C205" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="32" customHeight="1">
-      <c r="A206" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-8.1</t>
-        </is>
-      </c>
-      <c r="B206" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.5</t>
-        </is>
-      </c>
-      <c r="C206" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="32" customHeight="1">
-      <c r="A207" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-8.2</t>
-        </is>
-      </c>
-      <c r="B207" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.5</t>
-        </is>
-      </c>
-      <c r="C207" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="32" customHeight="1">
-      <c r="A208" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-8.2</t>
-        </is>
-      </c>
-      <c r="B208" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-02.2</t>
-        </is>
-      </c>
-      <c r="C208" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="32" customHeight="1">
-      <c r="A209" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-8.3</t>
-        </is>
-      </c>
-      <c r="B209" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.5</t>
-        </is>
-      </c>
-      <c r="C209" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="32" customHeight="1">
-      <c r="A210" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-8.3</t>
-        </is>
-      </c>
-      <c r="B210" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.6</t>
-        </is>
-      </c>
-      <c r="C210" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="32" customHeight="1">
-      <c r="A211" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-9.1</t>
-        </is>
-      </c>
-      <c r="B211" s="1" t="inlineStr">
-        <is>
-          <t>RC.RP-01.1</t>
-        </is>
-      </c>
-      <c r="C211" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="32" customHeight="1">
-      <c r="A212" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-9.1</t>
-        </is>
-      </c>
-      <c r="B212" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-04.1</t>
-        </is>
-      </c>
-      <c r="C212" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="16" customHeight="1">
-      <c r="A213" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-9.2</t>
-        </is>
-      </c>
-      <c r="B213" s="1" t="inlineStr">
-        <is>
-          <t>RC.RP-01.1</t>
-        </is>
-      </c>
-      <c r="C213" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="16" customHeight="1">
-      <c r="A214" s="1" t="inlineStr">
-        <is>
-          <t>PR.IP-9.2</t>
-        </is>
-      </c>
-      <c r="B214" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-04.2</t>
-        </is>
-      </c>
-      <c r="C214" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="16" customHeight="1">
-      <c r="A215" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.IP-11.1</t>
-        </is>
-      </c>
-      <c r="B215" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-04.1</t>
-        </is>
-      </c>
-      <c r="C215" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="16" customHeight="1">
-      <c r="A216" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.IP-11.1</t>
-        </is>
-      </c>
-      <c r="B216" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-04.2</t>
-        </is>
-      </c>
-      <c r="C216" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="32" customHeight="1">
-      <c r="A217" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-11.2</t>
-        </is>
-      </c>
-      <c r="B217" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-04.2</t>
-        </is>
-      </c>
-      <c r="C217" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="32" customHeight="1">
-      <c r="A218" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-11.2</t>
-        </is>
-      </c>
-      <c r="B218" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-04.1</t>
-        </is>
-      </c>
-      <c r="C218" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="32" customHeight="1">
-      <c r="A219" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-12.1</t>
-        </is>
-      </c>
-      <c r="B219" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-08.1</t>
-        </is>
-      </c>
-      <c r="C219" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="32" customHeight="1">
-      <c r="A220" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.IP-12.1</t>
-        </is>
-      </c>
-      <c r="B220" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-01.3</t>
-        </is>
-      </c>
-      <c r="C220" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="16" customHeight="1">
-      <c r="A221" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.MA-1.1</t>
-        </is>
-      </c>
-      <c r="B221" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.2</t>
-        </is>
-      </c>
-      <c r="C221" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="16" customHeight="1">
-      <c r="A222" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.MA-1.1</t>
-        </is>
-      </c>
-      <c r="B222" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.11</t>
-        </is>
-      </c>
-      <c r="C222" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="32" customHeight="1">
-      <c r="A223" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-1.2</t>
-        </is>
-      </c>
-      <c r="B223" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.6</t>
-        </is>
-      </c>
-      <c r="C223" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="32" customHeight="1">
-      <c r="A224" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-1.2</t>
-        </is>
-      </c>
-      <c r="B224" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.11</t>
-        </is>
-      </c>
-      <c r="C224" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="32" customHeight="1">
-      <c r="A225" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-1.3</t>
-        </is>
-      </c>
-      <c r="B225" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.8</t>
-        </is>
-      </c>
-      <c r="C225" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="32" customHeight="1">
-      <c r="A226" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-1.3</t>
-        </is>
-      </c>
-      <c r="B226" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.11</t>
-        </is>
-      </c>
-      <c r="C226" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="32" customHeight="1">
-      <c r="A227" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-1.4</t>
-        </is>
-      </c>
-      <c r="B227" s="1" t="inlineStr">
-        <is>
-          <t>D.AM-08.10</t>
-        </is>
-      </c>
-      <c r="C227" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="32" customHeight="1">
-      <c r="A228" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-1.4</t>
-        </is>
-      </c>
-      <c r="B228" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.11</t>
-        </is>
-      </c>
-      <c r="C228" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="16" customHeight="1">
-      <c r="A229" s="1" t="inlineStr">
-        <is>
-          <t>PR.MA-1.5</t>
-        </is>
-      </c>
-      <c r="B229" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.7</t>
-        </is>
-      </c>
-      <c r="C229" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="16" customHeight="1">
-      <c r="A230" s="1" t="inlineStr">
-        <is>
-          <t>PR.MA-1.5</t>
-        </is>
-      </c>
-      <c r="B230" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.11</t>
-        </is>
-      </c>
-      <c r="C230" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="16" customHeight="1">
-      <c r="A231" s="1" t="inlineStr">
-        <is>
-          <t>PR.MA-1.6</t>
-        </is>
-      </c>
-      <c r="B231" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.9</t>
-        </is>
-      </c>
-      <c r="C231" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="16" customHeight="1">
-      <c r="A232" s="1" t="inlineStr">
-        <is>
-          <t>PR.MA-1.6</t>
-        </is>
-      </c>
-      <c r="B232" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.11</t>
-        </is>
-      </c>
-      <c r="C232" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="16" customHeight="1">
-      <c r="A233" s="1" t="inlineStr">
-        <is>
-          <t>PR.MA-1.7</t>
-        </is>
-      </c>
-      <c r="B233" s="1" t="inlineStr">
-        <is>
-          <t>D.AM-08.10</t>
-        </is>
-      </c>
-      <c r="C233" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="16" customHeight="1">
-      <c r="A234" s="1" t="inlineStr">
-        <is>
-          <t>PR.MA-1.7</t>
-        </is>
-      </c>
-      <c r="B234" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.11</t>
-        </is>
-      </c>
-      <c r="C234" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="32" customHeight="1">
-      <c r="A235" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-2.1</t>
-        </is>
-      </c>
-      <c r="B235" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.11</t>
-        </is>
-      </c>
-      <c r="C235" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="32" customHeight="1">
-      <c r="A236" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-2.1</t>
-        </is>
-      </c>
-      <c r="B236" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.12</t>
-        </is>
-      </c>
-      <c r="C236" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="32" customHeight="1">
-      <c r="A237" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-2.2</t>
-        </is>
-      </c>
-      <c r="B237" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.12</t>
-        </is>
-      </c>
-      <c r="C237" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="32" customHeight="1">
-      <c r="A238" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.MA-2.2</t>
-        </is>
-      </c>
-      <c r="B238" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.3</t>
-        </is>
-      </c>
-      <c r="C238" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="16" customHeight="1">
-      <c r="A239" s="1" t="inlineStr">
-        <is>
-          <t>PR.MA-2.3</t>
-        </is>
-      </c>
-      <c r="B239" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.13</t>
-        </is>
-      </c>
-      <c r="C239" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="16" customHeight="1">
-      <c r="A240" s="1" t="inlineStr">
-        <is>
-          <t>PR.MA-2.3</t>
-        </is>
-      </c>
-      <c r="B240" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-08.11</t>
-        </is>
-      </c>
-      <c r="C240" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="16" customHeight="1">
-      <c r="A241" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.PT-1.1</t>
-        </is>
-      </c>
-      <c r="B241" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-04.1</t>
-        </is>
-      </c>
-      <c r="C241" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="16" customHeight="1">
-      <c r="A242" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.PT-1.1</t>
-        </is>
-      </c>
-      <c r="B242" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-04.5</t>
-        </is>
-      </c>
-      <c r="C242" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="32" customHeight="1">
-      <c r="A243" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.PT-1.2</t>
-        </is>
-      </c>
-      <c r="B243" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-04.2</t>
-        </is>
-      </c>
-      <c r="C243" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="16" customHeight="1">
-      <c r="A244" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-1.3</t>
-        </is>
-      </c>
-      <c r="B244" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-04.4</t>
-        </is>
-      </c>
-      <c r="C244" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="16" customHeight="1">
-      <c r="A245" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-1.4</t>
-        </is>
-      </c>
-      <c r="B245" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-04.5</t>
-        </is>
-      </c>
-      <c r="C245" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="32" customHeight="1">
-      <c r="A246" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.PT-2.1</t>
-        </is>
-      </c>
-      <c r="B246" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-01.5</t>
-        </is>
-      </c>
-      <c r="C246" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="32" customHeight="1">
-      <c r="A247" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.PT-2.1</t>
-        </is>
-      </c>
-      <c r="B247" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-01.4</t>
-        </is>
-      </c>
-      <c r="C247" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="32" customHeight="1">
-      <c r="A248" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.PT-2.2</t>
-        </is>
-      </c>
-      <c r="B248" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-01.5</t>
-        </is>
-      </c>
-      <c r="C248" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="16" customHeight="1">
-      <c r="A249" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-2.3</t>
-        </is>
-      </c>
-      <c r="B249" s="1" t="inlineStr">
-        <is>
-          <t>PR.DS-02.1</t>
-        </is>
-      </c>
-      <c r="C249" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="32" customHeight="1">
-      <c r="A250" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.PT-3.1</t>
-        </is>
-      </c>
-      <c r="B250" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.2</t>
-        </is>
-      </c>
-      <c r="C250" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="32" customHeight="1">
-      <c r="A251" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_PR.PT-3.1</t>
-        </is>
-      </c>
-      <c r="B251" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.3</t>
-        </is>
-      </c>
-      <c r="C251" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="16" customHeight="1">
-      <c r="A252" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-3.2</t>
-        </is>
-      </c>
-      <c r="B252" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.3</t>
-        </is>
-      </c>
-      <c r="C252" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="16" customHeight="1">
-      <c r="A253" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-3.2</t>
-        </is>
-      </c>
-      <c r="B253" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.2</t>
-        </is>
-      </c>
-      <c r="C253" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="16" customHeight="1">
-      <c r="A254" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-3.3</t>
-        </is>
-      </c>
-      <c r="B254" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.4</t>
-        </is>
-      </c>
-      <c r="C254" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="16" customHeight="1">
-      <c r="A255" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-3.3</t>
-        </is>
-      </c>
-      <c r="B255" s="1" t="inlineStr">
-        <is>
-          <t>PR.AA-03.3</t>
-        </is>
-      </c>
-      <c r="C255" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="16" customHeight="1">
-      <c r="A256" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_PR.PT-4.1</t>
-        </is>
-      </c>
-      <c r="B256" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-05.1</t>
-        </is>
-      </c>
-      <c r="C256" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="16" customHeight="1">
-      <c r="A257" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-4.2</t>
-        </is>
-      </c>
-      <c r="B257" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.8</t>
-        </is>
-      </c>
-      <c r="C257" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="16" customHeight="1">
-      <c r="A258" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-4.2</t>
-        </is>
-      </c>
-      <c r="B258" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.3</t>
-        </is>
-      </c>
-      <c r="C258" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="16" customHeight="1">
-      <c r="A259" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-4.3</t>
-        </is>
-      </c>
-      <c r="B259" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.9</t>
-        </is>
-      </c>
-      <c r="C259" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="16" customHeight="1">
-      <c r="A260" s="1" t="inlineStr">
-        <is>
-          <t>PR.PT-4.3</t>
-        </is>
-      </c>
-      <c r="B260" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.8</t>
-        </is>
-      </c>
-      <c r="C260" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="16" customHeight="1">
-      <c r="A261" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-1.1</t>
-        </is>
-      </c>
-      <c r="B261" s="1" t="inlineStr">
-        <is>
-          <t>PR.PS-01.1</t>
-        </is>
-      </c>
-      <c r="C261" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="32" customHeight="1">
-      <c r="A262" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.AE-2.1</t>
-        </is>
-      </c>
-      <c r="B262" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-02.1</t>
-        </is>
-      </c>
-      <c r="C262" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="16" customHeight="1">
-      <c r="A263" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-2.2</t>
-        </is>
-      </c>
-      <c r="B263" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-02.2</t>
-        </is>
-      </c>
-      <c r="C263" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="16" customHeight="1">
-      <c r="A264" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_DE.AE-3.1</t>
-        </is>
-      </c>
-      <c r="B264" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-03.1</t>
-        </is>
-      </c>
-      <c r="C264" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="265" ht="32" customHeight="1">
-      <c r="A265" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.AE-3.2</t>
-        </is>
-      </c>
-      <c r="B265" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-03.2</t>
-        </is>
-      </c>
-      <c r="C265" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="266" ht="16" customHeight="1">
-      <c r="A266" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-3.3</t>
-        </is>
-      </c>
-      <c r="B266" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-03.3</t>
-        </is>
-      </c>
-      <c r="C266" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="267" ht="16" customHeight="1">
-      <c r="A267" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-4.1</t>
-        </is>
-      </c>
-      <c r="B267" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-04.1</t>
-        </is>
-      </c>
-      <c r="C267" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="32" customHeight="1">
-      <c r="A268" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.AE-5.1</t>
-        </is>
-      </c>
-      <c r="B268" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.4</t>
-        </is>
-      </c>
-      <c r="C268" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="269" ht="32" customHeight="1">
-      <c r="A269" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.AE-5.1</t>
-        </is>
-      </c>
-      <c r="B269" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-08.2</t>
-        </is>
-      </c>
-      <c r="C269" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="270" ht="32" customHeight="1">
-      <c r="A270" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.AE-5.2</t>
-        </is>
-      </c>
-      <c r="B270" s="1" t="inlineStr">
-        <is>
-          <t>RS.MA-03.1</t>
-        </is>
-      </c>
-      <c r="C270" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="32" customHeight="1">
-      <c r="A271" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.AE-5.2</t>
-        </is>
-      </c>
-      <c r="B271" s="1" t="inlineStr">
-        <is>
-          <t>RS.MI-01.2</t>
-        </is>
-      </c>
-      <c r="C271" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="16" customHeight="1">
-      <c r="A272" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_DE.CM-1.1</t>
-        </is>
-      </c>
-      <c r="B272" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-01.1</t>
-        </is>
-      </c>
-      <c r="C272" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="32" customHeight="1">
-      <c r="A273" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-1.2</t>
-        </is>
-      </c>
-      <c r="B273" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-01.3</t>
-        </is>
-      </c>
-      <c r="C273" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="16" customHeight="1">
-      <c r="A274" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-1.3</t>
-        </is>
-      </c>
-      <c r="B274" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-01.4</t>
-        </is>
-      </c>
-      <c r="C274" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="16" customHeight="1">
-      <c r="A275" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-1.3</t>
-        </is>
-      </c>
-      <c r="B275" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-01.3</t>
-        </is>
-      </c>
-      <c r="C275" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="276" ht="32" customHeight="1">
-      <c r="A276" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-2.1</t>
-        </is>
-      </c>
-      <c r="B276" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-02.2</t>
-        </is>
-      </c>
-      <c r="C276" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="32" customHeight="1">
-      <c r="A277" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-2.1</t>
-        </is>
-      </c>
-      <c r="B277" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.1</t>
-        </is>
-      </c>
-      <c r="C277" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="278" ht="16" customHeight="1">
-      <c r="A278" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-2.2</t>
-        </is>
-      </c>
-      <c r="B278" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-02.2</t>
-        </is>
-      </c>
-      <c r="C278" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="279" ht="16" customHeight="1">
-      <c r="A279" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_DE.CM-3.1</t>
-        </is>
-      </c>
-      <c r="B279" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-03-1</t>
-        </is>
-      </c>
-      <c r="C279" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="280" ht="32" customHeight="1">
-      <c r="A280" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-3.2</t>
-        </is>
-      </c>
-      <c r="B280" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-03-2</t>
-        </is>
-      </c>
-      <c r="C280" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="32" customHeight="1">
-      <c r="A281" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-3.3</t>
-        </is>
-      </c>
-      <c r="B281" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-03-2</t>
-        </is>
-      </c>
-      <c r="C281" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="32" customHeight="1">
-      <c r="A282" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-3.3</t>
-        </is>
-      </c>
-      <c r="B282" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-03-1</t>
-        </is>
-      </c>
-      <c r="C282" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="16" customHeight="1">
-      <c r="A283" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_DE.CM-4.1</t>
-        </is>
-      </c>
-      <c r="B283" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-01.2</t>
-        </is>
-      </c>
-      <c r="C283" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" ht="16" customHeight="1">
-      <c r="A284" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-4.2</t>
-        </is>
-      </c>
-      <c r="B284" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.4</t>
-        </is>
-      </c>
-      <c r="C284" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="16" customHeight="1">
-      <c r="A285" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-4.2</t>
-        </is>
-      </c>
-      <c r="B285" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.5</t>
-        </is>
-      </c>
-      <c r="C285" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="32" customHeight="1">
-      <c r="A286" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-5.1</t>
-        </is>
-      </c>
-      <c r="B286" s="1" t="inlineStr">
-        <is>
-          <t>PR.IR-01.9</t>
-        </is>
-      </c>
-      <c r="C286" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="287" ht="32" customHeight="1">
-      <c r="A287" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-5.1</t>
-        </is>
-      </c>
-      <c r="B287" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.4</t>
-        </is>
-      </c>
-      <c r="C287" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="32" customHeight="1">
-      <c r="A288" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-6.1</t>
-        </is>
-      </c>
-      <c r="B288" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-06.2</t>
-        </is>
-      </c>
-      <c r="C288" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" ht="32" customHeight="1">
-      <c r="A289" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-6.1</t>
-        </is>
-      </c>
-      <c r="B289" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-06.1</t>
-        </is>
-      </c>
-      <c r="C289" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="290" ht="32" customHeight="1">
-      <c r="A290" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-6.2</t>
-        </is>
-      </c>
-      <c r="B290" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-06.2</t>
-        </is>
-      </c>
-      <c r="C290" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="291" ht="32" customHeight="1">
-      <c r="A291" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-7.1</t>
-        </is>
-      </c>
-      <c r="B291" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-01.3</t>
-        </is>
-      </c>
-      <c r="C291" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="32" customHeight="1">
-      <c r="A292" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-7.1</t>
-        </is>
-      </c>
-      <c r="B292" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-03-2</t>
-        </is>
-      </c>
-      <c r="C292" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="16" customHeight="1">
-      <c r="A293" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-7.2</t>
-        </is>
-      </c>
-      <c r="B293" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-01.3</t>
-        </is>
-      </c>
-      <c r="C293" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="16" customHeight="1">
-      <c r="A294" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-7.2</t>
-        </is>
-      </c>
-      <c r="B294" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-03-2</t>
-        </is>
-      </c>
-      <c r="C294" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="32" customHeight="1">
-      <c r="A295" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-8.1</t>
-        </is>
-      </c>
-      <c r="B295" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-01.4</t>
-        </is>
-      </c>
-      <c r="C295" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="32" customHeight="1">
-      <c r="A296" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-8.1</t>
-        </is>
-      </c>
-      <c r="B296" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-01.2</t>
-        </is>
-      </c>
-      <c r="C296" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="297" ht="32" customHeight="1">
-      <c r="A297" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.CM-8.2</t>
-        </is>
-      </c>
-      <c r="B297" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-08.2</t>
-        </is>
-      </c>
-      <c r="C297" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="32" customHeight="1">
-      <c r="A298" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.DP-2.1</t>
-        </is>
-      </c>
-      <c r="B298" s="1" t="inlineStr">
-        <is>
-          <t>GV.OC-03.2</t>
-        </is>
-      </c>
-      <c r="C298" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="299" ht="32" customHeight="1">
-      <c r="A299" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.DP-3.1</t>
-        </is>
-      </c>
-      <c r="B299" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.9</t>
-        </is>
-      </c>
-      <c r="C299" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="300" ht="32" customHeight="1">
-      <c r="A300" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.DP-3.1</t>
-        </is>
-      </c>
-      <c r="B300" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.4</t>
-        </is>
-      </c>
-      <c r="C300" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="301" ht="32" customHeight="1">
-      <c r="A301" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.DP-4.1</t>
-        </is>
-      </c>
-      <c r="B301" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-06.1</t>
-        </is>
-      </c>
-      <c r="C301" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="302" ht="32" customHeight="1">
-      <c r="A302" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.DP-4.1</t>
-        </is>
-      </c>
-      <c r="B302" s="1" t="inlineStr">
-        <is>
-          <t>RS.CO-02.1</t>
-        </is>
-      </c>
-      <c r="C302" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="32" customHeight="1">
-      <c r="A303" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.DP-5.1</t>
-        </is>
-      </c>
-      <c r="B303" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.5</t>
-        </is>
-      </c>
-      <c r="C303" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="32" customHeight="1">
-      <c r="A304" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_DE.DP-5.1</t>
-        </is>
-      </c>
-      <c r="B304" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.3</t>
-        </is>
-      </c>
-      <c r="C304" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="305" ht="16" customHeight="1">
-      <c r="A305" s="1" t="inlineStr">
-        <is>
-          <t>DE.DP-5.2</t>
-        </is>
-      </c>
-      <c r="B305" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.9</t>
-        </is>
-      </c>
-      <c r="C305" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="16" customHeight="1">
-      <c r="A306" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_RS.RP-1.1</t>
-        </is>
-      </c>
-      <c r="B306" s="1" t="inlineStr">
-        <is>
-          <t>RS.MA-01.1</t>
-        </is>
-      </c>
-      <c r="C306" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="307" ht="32" customHeight="1">
-      <c r="A307" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-1.1</t>
-        </is>
-      </c>
-      <c r="B307" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-01.3</t>
-        </is>
-      </c>
-      <c r="C307" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="308" ht="32" customHeight="1">
-      <c r="A308" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-1.1</t>
-        </is>
-      </c>
-      <c r="B308" s="1" t="inlineStr">
-        <is>
-          <t>GV.RR-02.1</t>
-        </is>
-      </c>
-      <c r="C308" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="309" ht="32" customHeight="1">
-      <c r="A309" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-2.1</t>
-        </is>
-      </c>
-      <c r="B309" s="1" t="inlineStr">
-        <is>
-          <t>RS.MA-02.1</t>
-        </is>
-      </c>
-      <c r="C309" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="310" ht="32" customHeight="1">
-      <c r="A310" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-2.1</t>
-        </is>
-      </c>
-      <c r="B310" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-08.1</t>
-        </is>
-      </c>
-      <c r="C310" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="311" ht="16" customHeight="1">
-      <c r="A311" s="1" t="inlineStr">
-        <is>
-          <t>RS.CO-2.2</t>
-        </is>
-      </c>
-      <c r="B311" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-08.1</t>
-        </is>
-      </c>
-      <c r="C311" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="312" ht="16" customHeight="1">
-      <c r="A312" s="1" t="inlineStr">
-        <is>
-          <t>RS.CO-2.2</t>
-        </is>
-      </c>
-      <c r="B312" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-02.1</t>
-        </is>
-      </c>
-      <c r="C312" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="313" ht="16" customHeight="1">
-      <c r="A313" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_RS.CO-3.1</t>
-        </is>
-      </c>
-      <c r="B313" s="1" t="inlineStr">
-        <is>
-          <t>RC.CO-04.3</t>
-        </is>
-      </c>
-      <c r="C313" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="16" customHeight="1">
-      <c r="A314" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_RS.CO-3.1</t>
-        </is>
-      </c>
-      <c r="B314" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-04.2</t>
-        </is>
-      </c>
-      <c r="C314" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="32" customHeight="1">
-      <c r="A315" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-3.2</t>
-        </is>
-      </c>
-      <c r="B315" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-04.2</t>
-        </is>
-      </c>
-      <c r="C315" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="316" ht="32" customHeight="1">
-      <c r="A316" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-3.2</t>
-        </is>
-      </c>
-      <c r="B316" s="1" t="inlineStr">
-        <is>
-          <t>RS.MA-01.2</t>
-        </is>
-      </c>
-      <c r="C316" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="317" ht="32" customHeight="1">
-      <c r="A317" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-4.1</t>
-        </is>
-      </c>
-      <c r="B317" s="1" t="inlineStr">
-        <is>
-          <t>RS.MA-01.2</t>
-        </is>
-      </c>
-      <c r="C317" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="318" ht="32" customHeight="1">
-      <c r="A318" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-4.1</t>
-        </is>
-      </c>
-      <c r="B318" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-04.2</t>
-        </is>
-      </c>
-      <c r="C318" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="319" ht="32" customHeight="1">
-      <c r="A319" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-5.1</t>
-        </is>
-      </c>
-      <c r="B319" s="1" t="inlineStr">
-        <is>
-          <t>RS.CO-02.1</t>
-        </is>
-      </c>
-      <c r="C319" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="320" ht="32" customHeight="1">
-      <c r="A320" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.CO-5.1</t>
-        </is>
-      </c>
-      <c r="B320" s="1" t="inlineStr">
-        <is>
-          <t>RS.CO-02.2</t>
-        </is>
-      </c>
-      <c r="C320" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="321" ht="32" customHeight="1">
-      <c r="A321" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.AN-1.1</t>
-        </is>
-      </c>
-      <c r="B321" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.4</t>
-        </is>
-      </c>
-      <c r="C321" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="322" ht="32" customHeight="1">
-      <c r="A322" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.AN-1.1</t>
-        </is>
-      </c>
-      <c r="B322" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-02.2</t>
-        </is>
-      </c>
-      <c r="C322" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="323" ht="16" customHeight="1">
-      <c r="A323" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-1.2</t>
-        </is>
-      </c>
-      <c r="B323" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-02.2</t>
-        </is>
-      </c>
-      <c r="C323" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="324" ht="16" customHeight="1">
-      <c r="A324" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-1.2</t>
-        </is>
-      </c>
-      <c r="B324" s="1" t="inlineStr">
-        <is>
-          <t>DE.CM-09.4</t>
-        </is>
-      </c>
-      <c r="C324" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="325" ht="32" customHeight="1">
-      <c r="A325" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.AN-2.1</t>
-        </is>
-      </c>
-      <c r="B325" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-02.1</t>
-        </is>
-      </c>
-      <c r="C325" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="32" customHeight="1">
-      <c r="A326" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.AN-2.1</t>
-        </is>
-      </c>
-      <c r="B326" s="1" t="inlineStr">
-        <is>
-          <t>PR.AT-02.1</t>
-        </is>
-      </c>
-      <c r="C326" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="327" ht="16" customHeight="1">
-      <c r="A327" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-2.2</t>
-        </is>
-      </c>
-      <c r="B327" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-04.1</t>
-        </is>
-      </c>
-      <c r="C327" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="328" ht="16" customHeight="1">
-      <c r="A328" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-2.2</t>
-        </is>
-      </c>
-      <c r="B328" s="1" t="inlineStr">
-        <is>
-          <t>DE.AE-02.2</t>
-        </is>
-      </c>
-      <c r="C328" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="329" ht="16" customHeight="1">
-      <c r="A329" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-3.1</t>
-        </is>
-      </c>
-      <c r="B329" s="1" t="inlineStr">
-        <is>
-          <t>RS.MA-02.2</t>
-        </is>
-      </c>
-      <c r="C329" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="330" ht="16" customHeight="1">
-      <c r="A330" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-3.1</t>
-        </is>
-      </c>
-      <c r="B330" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.1</t>
-        </is>
-      </c>
-      <c r="C330" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="331" ht="16" customHeight="1">
-      <c r="A331" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-3.2</t>
-        </is>
-      </c>
-      <c r="B331" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-03.1</t>
-        </is>
-      </c>
-      <c r="C331" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="332" ht="16" customHeight="1">
-      <c r="A332" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-3.2</t>
-        </is>
-      </c>
-      <c r="B332" s="1" t="inlineStr">
-        <is>
-          <t>RS.MI-01.2</t>
-        </is>
-      </c>
-      <c r="C332" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="333" ht="32" customHeight="1">
-      <c r="A333" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.AN-4.1</t>
-        </is>
-      </c>
-      <c r="B333" s="1" t="inlineStr">
-        <is>
-          <t>RS.MA-03.1</t>
-        </is>
-      </c>
-      <c r="C333" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="334" ht="32" customHeight="1">
-      <c r="A334" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.AN-5.1</t>
-        </is>
-      </c>
-      <c r="B334" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-08.2</t>
-        </is>
-      </c>
-      <c r="C334" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="335" ht="32" customHeight="1">
-      <c r="A335" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.AN-5.1</t>
-        </is>
-      </c>
-      <c r="B335" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-08.1</t>
-        </is>
-      </c>
-      <c r="C335" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="336" ht="16" customHeight="1">
-      <c r="A336" s="1" t="inlineStr">
-        <is>
-          <t>RS.AN-5.2</t>
-        </is>
-      </c>
-      <c r="B336" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-08.2</t>
-        </is>
-      </c>
-      <c r="C336" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="337" ht="32" customHeight="1">
-      <c r="A337" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.MI-1.1</t>
-        </is>
-      </c>
-      <c r="B337" s="1" t="inlineStr">
-        <is>
-          <t>RS.MI-01.1</t>
-        </is>
-      </c>
-      <c r="C337" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="338" ht="32" customHeight="1">
-      <c r="A338" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.MI-1.1</t>
-        </is>
-      </c>
-      <c r="B338" s="1" t="inlineStr">
-        <is>
-          <t>RS.MI-01.2</t>
-        </is>
-      </c>
-      <c r="C338" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="339" ht="32" customHeight="1">
-      <c r="A339" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.MI-1.1</t>
-        </is>
-      </c>
-      <c r="B339" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-08.1</t>
-        </is>
-      </c>
-      <c r="C339" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="340" ht="32" customHeight="1">
-      <c r="A340" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.MI-1.1</t>
-        </is>
-      </c>
-      <c r="B340" s="1" t="inlineStr">
-        <is>
-          <t>ID.RA-08.2</t>
-        </is>
-      </c>
-      <c r="C340" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="341" ht="16" customHeight="1">
-      <c r="A341" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_RS.IM-1.1</t>
-        </is>
-      </c>
-      <c r="B341" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.1</t>
-        </is>
-      </c>
-      <c r="C341" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="16" customHeight="1">
-      <c r="A342" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_RS.IM-1.1</t>
-        </is>
-      </c>
-      <c r="B342" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-04.2</t>
-        </is>
-      </c>
-      <c r="C342" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="32" customHeight="1">
-      <c r="A343" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.IM-1.2</t>
-        </is>
-      </c>
-      <c r="B343" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.2</t>
-        </is>
-      </c>
-      <c r="C343" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="344" ht="32" customHeight="1">
-      <c r="A344" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.IM-2.1</t>
-        </is>
-      </c>
-      <c r="B344" s="1" t="inlineStr">
-        <is>
-          <t>RC.CO-03.1</t>
-        </is>
-      </c>
-      <c r="C344" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="345" ht="32" customHeight="1">
-      <c r="A345" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RS.IM-2.1</t>
-        </is>
-      </c>
-      <c r="B345" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-04.2</t>
-        </is>
-      </c>
-      <c r="C345" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="16" customHeight="1">
-      <c r="A346" s="1" t="inlineStr">
-        <is>
-          <t>BASIC_RC.RP-1.1</t>
-        </is>
-      </c>
-      <c r="B346" s="1" t="inlineStr">
-        <is>
-          <t>RC.RP-01.1</t>
-        </is>
-      </c>
-      <c r="C346" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="347" ht="16" customHeight="1">
-      <c r="A347" s="1" t="inlineStr">
-        <is>
-          <t>RC.RP-1.2</t>
-        </is>
-      </c>
-      <c r="B347" s="1" t="inlineStr">
-        <is>
-          <t>RC.RP-01.1</t>
-        </is>
-      </c>
-      <c r="C347" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="348" ht="16" customHeight="1">
-      <c r="A348" s="1" t="inlineStr">
-        <is>
-          <t>RC.RP-1.2</t>
-        </is>
-      </c>
-      <c r="B348" s="1" t="inlineStr">
-        <is>
-          <t>RC.RP-02.1</t>
-        </is>
-      </c>
-      <c r="C348" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="349" ht="32" customHeight="1">
-      <c r="A349" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RC.IM-1.1</t>
-        </is>
-      </c>
-      <c r="B349" s="1" t="inlineStr">
-        <is>
-          <t>RC.RP-01.1</t>
-        </is>
-      </c>
-      <c r="C349" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="350" ht="32" customHeight="1">
-      <c r="A350" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RC.IM-1.1</t>
-        </is>
-      </c>
-      <c r="B350" s="1" t="inlineStr">
-        <is>
-          <t>ID.IM-03.2</t>
-        </is>
-      </c>
-      <c r="C350" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="351" ht="32" customHeight="1">
-      <c r="A351" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RC.CO-1.1</t>
-        </is>
-      </c>
-      <c r="B351" s="1" t="inlineStr">
-        <is>
-          <t>RC.CO-04.2</t>
-        </is>
-      </c>
-      <c r="C351" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="352" ht="32" customHeight="1">
-      <c r="A352" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RC.CO-1.1</t>
-        </is>
-      </c>
-      <c r="B352" s="1" t="inlineStr">
-        <is>
-          <t>ID.AM-02.3</t>
-        </is>
-      </c>
-      <c r="C352" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="353" ht="16" customHeight="1">
-      <c r="A353" s="1" t="inlineStr">
-        <is>
-          <t>RC.CO-1.2</t>
-        </is>
-      </c>
-      <c r="B353" s="1" t="inlineStr">
-        <is>
-          <t>RC.CO-04.2</t>
-        </is>
-      </c>
-      <c r="C353" s="1" t="inlineStr">
-        <is>
-          <t>equal</t>
-        </is>
-      </c>
-    </row>
-    <row r="354" ht="16" customHeight="1">
-      <c r="A354" s="1" t="inlineStr">
-        <is>
-          <t>RC.CO-2.1</t>
-        </is>
-      </c>
-      <c r="B354" s="1" t="inlineStr">
-        <is>
-          <t>RC.CO-04.3</t>
-        </is>
-      </c>
-      <c r="C354" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
-    <row r="355" ht="32" customHeight="1">
-      <c r="A355" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT_RC.CO-3.1</t>
-        </is>
-      </c>
-      <c r="B355" s="1" t="inlineStr">
-        <is>
-          <t>RC.CO-03.1</t>
-        </is>
-      </c>
-      <c r="C355" s="1" t="inlineStr">
-        <is>
-          <t>intersect</t>
-        </is>
-      </c>
-    </row>
+    <row r="197" ht="32" customHeight="1"/>
+    <row r="198" ht="16" customHeight="1"/>
+    <row r="199" ht="16" customHeight="1"/>
+    <row r="200" ht="32" customHeight="1"/>
+    <row r="201" ht="32" customHeight="1"/>
+    <row r="202" ht="16" customHeight="1"/>
+    <row r="203" ht="16" customHeight="1"/>
+    <row r="204" ht="16" customHeight="1"/>
+    <row r="205" ht="32" customHeight="1"/>
+    <row r="206" ht="32" customHeight="1"/>
+    <row r="207" ht="32" customHeight="1"/>
+    <row r="208" ht="32" customHeight="1"/>
+    <row r="209" ht="32" customHeight="1"/>
+    <row r="210" ht="32" customHeight="1"/>
+    <row r="211" ht="32" customHeight="1"/>
+    <row r="212" ht="32" customHeight="1"/>
+    <row r="213" ht="16" customHeight="1"/>
+    <row r="214" ht="16" customHeight="1"/>
+    <row r="215" ht="16" customHeight="1"/>
+    <row r="216" ht="16" customHeight="1"/>
+    <row r="217" ht="32" customHeight="1"/>
+    <row r="218" ht="32" customHeight="1"/>
+    <row r="219" ht="32" customHeight="1"/>
+    <row r="220" ht="32" customHeight="1"/>
+    <row r="221" ht="16" customHeight="1"/>
+    <row r="222" ht="16" customHeight="1"/>
+    <row r="223" ht="32" customHeight="1"/>
+    <row r="224" ht="32" customHeight="1"/>
+    <row r="225" ht="32" customHeight="1"/>
+    <row r="226" ht="32" customHeight="1"/>
+    <row r="227" ht="32" customHeight="1"/>
+    <row r="228" ht="32" customHeight="1"/>
+    <row r="229" ht="16" customHeight="1"/>
+    <row r="230" ht="16" customHeight="1"/>
+    <row r="231" ht="16" customHeight="1"/>
+    <row r="232" ht="16" customHeight="1"/>
+    <row r="233" ht="16" customHeight="1"/>
+    <row r="234" ht="16" customHeight="1"/>
+    <row r="235" ht="32" customHeight="1"/>
+    <row r="236" ht="32" customHeight="1"/>
+    <row r="237" ht="32" customHeight="1"/>
+    <row r="238" ht="32" customHeight="1"/>
+    <row r="239" ht="16" customHeight="1"/>
+    <row r="240" ht="16" customHeight="1"/>
+    <row r="241" ht="16" customHeight="1"/>
+    <row r="242" ht="16" customHeight="1"/>
+    <row r="243" ht="32" customHeight="1"/>
+    <row r="244" ht="16" customHeight="1"/>
+    <row r="245" ht="16" customHeight="1"/>
+    <row r="246" ht="32" customHeight="1"/>
+    <row r="247" ht="32" customHeight="1"/>
+    <row r="248" ht="32" customHeight="1"/>
+    <row r="249" ht="16" customHeight="1"/>
+    <row r="250" ht="32" customHeight="1"/>
+    <row r="251" ht="32" customHeight="1"/>
+    <row r="252" ht="16" customHeight="1"/>
+    <row r="253" ht="16" customHeight="1"/>
+    <row r="254" ht="16" customHeight="1"/>
+    <row r="255" ht="16" customHeight="1"/>
+    <row r="256" ht="16" customHeight="1"/>
+    <row r="257" ht="16" customHeight="1"/>
+    <row r="258" ht="16" customHeight="1"/>
+    <row r="259" ht="16" customHeight="1"/>
+    <row r="260" ht="16" customHeight="1"/>
+    <row r="261" ht="16" customHeight="1"/>
+    <row r="262" ht="32" customHeight="1"/>
+    <row r="263" ht="16" customHeight="1"/>
+    <row r="264" ht="16" customHeight="1"/>
+    <row r="265" ht="32" customHeight="1"/>
+    <row r="266" ht="16" customHeight="1"/>
+    <row r="267" ht="16" customHeight="1"/>
+    <row r="268" ht="32" customHeight="1"/>
+    <row r="269" ht="32" customHeight="1"/>
+    <row r="270" ht="32" customHeight="1"/>
+    <row r="271" ht="32" customHeight="1"/>
+    <row r="272" ht="16" customHeight="1"/>
+    <row r="273" ht="32" customHeight="1"/>
+    <row r="274" ht="16" customHeight="1"/>
+    <row r="275" ht="16" customHeight="1"/>
+    <row r="276" ht="32" customHeight="1"/>
+    <row r="277" ht="32" customHeight="1"/>
+    <row r="278" ht="16" customHeight="1"/>
+    <row r="279" ht="16" customHeight="1"/>
+    <row r="280" ht="32" customHeight="1"/>
+    <row r="281" ht="32" customHeight="1"/>
+    <row r="282" ht="32" customHeight="1"/>
+    <row r="283" ht="16" customHeight="1"/>
+    <row r="284" ht="16" customHeight="1"/>
+    <row r="285" ht="16" customHeight="1"/>
+    <row r="286" ht="32" customHeight="1"/>
+    <row r="287" ht="32" customHeight="1"/>
+    <row r="288" ht="32" customHeight="1"/>
+    <row r="289" ht="32" customHeight="1"/>
+    <row r="290" ht="32" customHeight="1"/>
+    <row r="291" ht="32" customHeight="1"/>
+    <row r="292" ht="32" customHeight="1"/>
+    <row r="293" ht="16" customHeight="1"/>
+    <row r="294" ht="16" customHeight="1"/>
+    <row r="295" ht="32" customHeight="1"/>
+    <row r="296" ht="32" customHeight="1"/>
+    <row r="297" ht="32" customHeight="1"/>
+    <row r="298" ht="32" customHeight="1"/>
+    <row r="299" ht="32" customHeight="1"/>
+    <row r="300" ht="32" customHeight="1"/>
+    <row r="301" ht="32" customHeight="1"/>
+    <row r="302" ht="32" customHeight="1"/>
+    <row r="303" ht="32" customHeight="1"/>
+    <row r="304" ht="32" customHeight="1"/>
+    <row r="305" ht="16" customHeight="1"/>
+    <row r="306" ht="16" customHeight="1"/>
+    <row r="307" ht="32" customHeight="1"/>
+    <row r="308" ht="32" customHeight="1"/>
+    <row r="309" ht="32" customHeight="1"/>
+    <row r="310" ht="32" customHeight="1"/>
+    <row r="311" ht="16" customHeight="1"/>
+    <row r="312" ht="16" customHeight="1"/>
+    <row r="313" ht="16" customHeight="1"/>
+    <row r="314" ht="16" customHeight="1"/>
+    <row r="315" ht="32" customHeight="1"/>
+    <row r="316" ht="32" customHeight="1"/>
+    <row r="317" ht="32" customHeight="1"/>
+    <row r="318" ht="32" customHeight="1"/>
+    <row r="319" ht="32" customHeight="1"/>
+    <row r="320" ht="32" customHeight="1"/>
+    <row r="321" ht="32" customHeight="1"/>
+    <row r="322" ht="32" customHeight="1"/>
+    <row r="323" ht="16" customHeight="1"/>
+    <row r="324" ht="16" customHeight="1"/>
+    <row r="325" ht="32" customHeight="1"/>
+    <row r="326" ht="32" customHeight="1"/>
+    <row r="327" ht="16" customHeight="1"/>
+    <row r="328" ht="16" customHeight="1"/>
+    <row r="329" ht="16" customHeight="1"/>
+    <row r="330" ht="16" customHeight="1"/>
+    <row r="331" ht="16" customHeight="1"/>
+    <row r="332" ht="16" customHeight="1"/>
+    <row r="333" ht="32" customHeight="1"/>
+    <row r="334" ht="32" customHeight="1"/>
+    <row r="335" ht="32" customHeight="1"/>
+    <row r="336" ht="16" customHeight="1"/>
+    <row r="337" ht="32" customHeight="1"/>
+    <row r="338" ht="32" customHeight="1"/>
+    <row r="339" ht="32" customHeight="1"/>
+    <row r="340" ht="32" customHeight="1"/>
+    <row r="341" ht="16" customHeight="1"/>
+    <row r="342" ht="16" customHeight="1"/>
+    <row r="343" ht="32" customHeight="1"/>
+    <row r="344" ht="32" customHeight="1"/>
+    <row r="345" ht="32" customHeight="1"/>
+    <row r="346" ht="16" customHeight="1"/>
+    <row r="347" ht="16" customHeight="1"/>
+    <row r="348" ht="16" customHeight="1"/>
+    <row r="349" ht="32" customHeight="1"/>
+    <row r="350" ht="32" customHeight="1"/>
+    <row r="351" ht="32" customHeight="1"/>
+    <row r="352" ht="32" customHeight="1"/>
+    <row r="353" ht="16" customHeight="1"/>
+    <row r="354" ht="16" customHeight="1"/>
+    <row r="355" ht="32" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
